--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ARIZONA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ARIZONA_2022.xlsx
@@ -2353,7 +2353,7 @@
         <v>139</v>
       </c>
       <c r="D111">
-        <v>0.009453210010881393</v>
+        <v>0.009453210010881391</v>
       </c>
     </row>
     <row r="112">
@@ -2677,7 +2677,7 @@
         <v>141</v>
       </c>
       <c r="D129">
-        <v>0.009589227421109903</v>
+        <v>0.009589227421109904</v>
       </c>
     </row>
     <row r="130">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C156">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C313">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C322">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C793">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C794">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C821">
